--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486822_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486822_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5999</v>
+        <v>3.5739</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5745</v>
+        <v>2.7471</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0254</v>
+        <v>0.8268</v>
       </c>
       <c r="G2" t="n">
         <v>2.9367</v>
@@ -610,13 +610,13 @@
         <v>1.3515</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6053</v>
+        <v>0.5792</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5993</v>
+        <v>0.772</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0059</v>
+        <v>-0.1927</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3282</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Y. BOUBACAR</t>
+          <t>S. KONTE SYLLA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8401</v>
+        <v>0.2403</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2508</v>
+        <v>1.1864</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.4107</v>
+        <v>-0.9461000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2128</v>
+        <v>0.3065</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7449</v>
+        <v>3.1526</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4679</v>
+        <v>-2.8462</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5243</v>
+        <v>2.3288</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2629</v>
+        <v>3.7055</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2615</v>
+        <v>-1.3767</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.3115</v>
+        <v>-2.0223</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.5179</v>
+        <v>-0.5528</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7935</v>
+        <v>-1.4695</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7723</v>
+        <v>0.5792</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7723</v>
+        <v>1.5446</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0827</v>
+        <v>-0.3172</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4409</v>
+        <v>0.1512</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3582</v>
+        <v>-0.4684</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.2277</v>
+        <v>-0.3282</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2856</v>
+        <v>-0.3282</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.5133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. KONTE SYLLA</t>
+          <t>Y. BOUBACAR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6458</v>
+        <v>-0.1114</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3932</v>
+        <v>3.4234</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7474</v>
+        <v>-3.5349</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3065</v>
+        <v>1.2128</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1526</v>
+        <v>0.7449</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.8462</v>
+        <v>0.4679</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3288</v>
+        <v>3.5243</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7055</v>
+        <v>2.2629</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.3767</v>
+        <v>1.2615</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0223</v>
+        <v>-2.3115</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5528</v>
+        <v>-1.5179</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.4695</v>
+        <v>-0.7935</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5792</v>
+        <v>0.7723</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5446</v>
+        <v>0.7723</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0883</v>
+        <v>-0.8689</v>
       </c>
       <c r="T4" t="n">
-        <v>0.358</v>
+        <v>-0.3865</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2697</v>
+        <v>-0.4824</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3282</v>
+        <v>-1.2277</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3282</v>
+        <v>0.2856</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="5">
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4218</v>
+        <v>-0.3184</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.118</v>
+        <v>-0.0145</v>
       </c>
       <c r="F5" t="n">
         <v>-0.3038</v>
@@ -844,10 +844,10 @@
         <v>0.5792</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0827</v>
+        <v>0.0207</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2207</v>
+        <v>-0.1173</v>
       </c>
       <c r="U5" t="n">
         <v>0.138</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.343</v>
+        <v>-1.8133</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.7842</v>
+        <v>-1.5773</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5588</v>
+        <v>-0.236</v>
       </c>
       <c r="G6" t="n">
         <v>-3.0428</v>
@@ -922,13 +922,13 @@
         <v>1.9308</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3847</v>
+        <v>-0.8551</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.497</v>
+        <v>-0.2902</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8877</v>
+        <v>-0.5649</v>
       </c>
       <c r="V6" t="n">
         <v>2.0845</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.3834</v>
+        <v>-3.2262</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8217</v>
+        <v>-1.6148</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.5617</v>
+        <v>-1.6114</v>
       </c>
       <c r="G7" t="n">
         <v>0.4663</v>
@@ -1000,13 +1000,13 @@
         <v>1.9308</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1434</v>
+        <v>0.0138</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3866</v>
+        <v>-0.1798</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2433</v>
+        <v>0.1936</v>
       </c>
       <c r="V7" t="n">
         <v>-2.741</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.8032</v>
+        <v>-5.0626</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.5235</v>
+        <v>-4.0064</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2797</v>
+        <v>-1.0562</v>
       </c>
       <c r="G8" t="n">
         <v>-1.3114</v>
@@ -1078,13 +1078,13 @@
         <v>0.9654</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.9472</v>
+        <v>-1.2066</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5795</v>
+        <v>-0.0624</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.3677</v>
+        <v>-1.1443</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6138</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.4996</v>
+        <v>-5.6474</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.6289</v>
+        <v>-2.8015</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.8707</v>
+        <v>-2.8459</v>
       </c>
       <c r="G9" t="n">
         <v>-7.0642</v>
@@ -1156,13 +1156,13 @@
         <v>1.5446</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.4933</v>
+        <v>-1.6411</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.5451</v>
+        <v>-0.7177</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9482</v>
+        <v>-0.9234</v>
       </c>
       <c r="V9" t="n">
         <v>1.5133</v>
@@ -1189,16 +1189,16 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-12.3652</v>
+        <v>-12.3651</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6578</v>
+        <v>-2.6576</v>
       </c>
       <c r="F10" t="n">
-        <v>-9.7074</v>
+        <v>-9.7075</v>
       </c>
       <c r="G10" t="n">
-        <v>-7.414399999999999</v>
+        <v>-7.414399999999998</v>
       </c>
       <c r="H10" t="n">
         <v>0.0008999999999996788</v>
@@ -1207,7 +1207,7 @@
         <v>-7.4152</v>
       </c>
       <c r="J10" t="n">
-        <v>3.700400000000002</v>
+        <v>3.7004</v>
       </c>
       <c r="K10" t="n">
         <v>7.249400000000001</v>
@@ -1234,13 +1234,13 @@
         <v>10.6192</v>
       </c>
       <c r="S10" t="n">
-        <v>-4.275</v>
+        <v>-4.2752</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8306999999999998</v>
+        <v>-0.8307</v>
       </c>
       <c r="U10" t="n">
-        <v>-3.4443</v>
+        <v>-3.4445</v>
       </c>
       <c r="V10" t="n">
         <v>-1.6411</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. KELLIER</t>
+          <t>J. KASA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>8.658899999999999</v>
+        <v>7.3659</v>
       </c>
       <c r="E11" t="n">
-        <v>7.2779</v>
+        <v>5.087</v>
       </c>
       <c r="F11" t="n">
-        <v>1.381</v>
+        <v>2.2789</v>
       </c>
       <c r="G11" t="n">
-        <v>2.185</v>
+        <v>3.1729</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6145</v>
+        <v>2.0064</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4295</v>
+        <v>1.1665</v>
       </c>
       <c r="J11" t="n">
-        <v>2.807</v>
+        <v>2.3465</v>
       </c>
       <c r="K11" t="n">
-        <v>4.7533</v>
+        <v>2.421</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9464</v>
+        <v>-0.0745</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.622</v>
+        <v>0.8264</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.1389</v>
+        <v>-0.4146</v>
       </c>
       <c r="O11" t="n">
-        <v>1.5169</v>
+        <v>1.2411</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7723</v>
+        <v>1.3515</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7377</v>
+        <v>1.3515</v>
       </c>
       <c r="S11" t="n">
-        <v>3.5744</v>
+        <v>0.9999</v>
       </c>
       <c r="T11" t="n">
-        <v>3.3091</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2653</v>
+        <v>0.3866</v>
       </c>
       <c r="V11" t="n">
-        <v>2.1271</v>
+        <v>1.8415</v>
       </c>
       <c r="W11" t="n">
         <v>2.1271</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. KASA</t>
+          <t>J. KELLIER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.817</v>
+        <v>6.8151</v>
       </c>
       <c r="E12" t="n">
-        <v>5.1904</v>
+        <v>5.5197</v>
       </c>
       <c r="F12" t="n">
-        <v>2.6266</v>
+        <v>1.2954</v>
       </c>
       <c r="G12" t="n">
-        <v>3.1729</v>
+        <v>2.185</v>
       </c>
       <c r="H12" t="n">
-        <v>2.0064</v>
+        <v>2.6145</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1665</v>
+        <v>-0.4295</v>
       </c>
       <c r="J12" t="n">
-        <v>2.3465</v>
+        <v>2.807</v>
       </c>
       <c r="K12" t="n">
-        <v>2.421</v>
+        <v>4.7533</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.0745</v>
+        <v>-1.9464</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8264</v>
+        <v>-0.622</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4146</v>
+        <v>-2.1389</v>
       </c>
       <c r="O12" t="n">
-        <v>1.2411</v>
+        <v>1.5169</v>
       </c>
       <c r="P12" t="n">
-        <v>1.3515</v>
+        <v>0.7723</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3515</v>
+        <v>1.7377</v>
       </c>
       <c r="S12" t="n">
-        <v>1.451</v>
+        <v>1.7307</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7168</v>
+        <v>1.551</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7342</v>
+        <v>0.1797</v>
       </c>
       <c r="V12" t="n">
-        <v>1.8415</v>
+        <v>2.1271</v>
       </c>
       <c r="W12" t="n">
         <v>2.1271</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.2568</v>
+        <v>4.0417</v>
       </c>
       <c r="E13" t="n">
-        <v>4.8007</v>
+        <v>4.387</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.544</v>
+        <v>-0.3453</v>
       </c>
       <c r="G13" t="n">
         <v>4.2348</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.022</v>
+        <v>-0.1931</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3032</v>
+        <v>-0.1105</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2813</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2706</v>
+        <v>3.3808</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1768</v>
+        <v>1.9007</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0939</v>
+        <v>1.4801</v>
       </c>
       <c r="G14" t="n">
         <v>1.1037</v>
@@ -1546,13 +1546,13 @@
         <v>1.9308</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7171999999999999</v>
+        <v>0.3929</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1934</v>
+        <v>0.5305</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5238</v>
+        <v>-0.1376</v>
       </c>
       <c r="V14" t="n">
         <v>1.8842</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.6347</v>
+        <v>0.5582</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2901</v>
+        <v>0.6407</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3445</v>
+        <v>-0.0825</v>
       </c>
       <c r="G15" t="n">
         <v>-0.6703</v>
@@ -1624,13 +1624,13 @@
         <v>1.9308</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.324</v>
+        <v>-0.1311</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7174</v>
+        <v>0.2134</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6066</v>
+        <v>-0.3445</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5712</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. VAQUERO PASCUAL</t>
+          <t>P. LOPEZ USO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.1725</v>
+        <v>-1.2345</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7161999999999999</v>
+        <v>-1.9135</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4563</v>
+        <v>0.679</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1175</v>
+        <v>-0.5491</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.786</v>
+        <v>0.5925</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9035</v>
+        <v>-1.1416</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3874</v>
+        <v>-0.9065</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.9577</v>
+        <v>0.3865</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3451</v>
+        <v>-1.293</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.27</v>
+        <v>0.3574</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8283</v>
+        <v>0.206</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5583</v>
+        <v>0.1514</v>
       </c>
       <c r="P16" t="n">
         <v>-0.9654</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9654</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.517</v>
+        <v>0.5655</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8270999999999999</v>
+        <v>-0.0417</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6898</v>
+        <v>0.6072</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.8415</v>
+        <v>-0.2856</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.8415</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. LOPEZ USO</t>
+          <t>J. BOONYASITH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.8054</v>
+        <v>-1.3051</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.5341</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7286</v>
+        <v>-0.7461</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5491</v>
+        <v>0.9087</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5925</v>
+        <v>1.6208</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.1416</v>
+        <v>-0.7121</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9065</v>
+        <v>1.1722</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3865</v>
+        <v>2.5873</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.293</v>
+        <v>-1.4151</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3574</v>
+        <v>-0.2635</v>
       </c>
       <c r="N17" t="n">
-        <v>0.206</v>
+        <v>-0.9665</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1514</v>
+        <v>0.703</v>
       </c>
       <c r="P17" t="n">
         <v>-0.9654</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.9654</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0053</v>
+        <v>-0.0207</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6622</v>
+        <v>0.1995</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6568000000000001</v>
+        <v>-0.2203</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2856</v>
+        <v>-1.2277</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2856</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. MUKENDI KABANGA</t>
+          <t>J. VAQUERO PASCUAL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.0963</v>
+        <v>-1.5862</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.912</v>
+        <v>-1.1299</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1843</v>
+        <v>-0.4563</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.8988</v>
+        <v>0.1175</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.5303</v>
+        <v>-1.786</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3685</v>
+        <v>1.9035</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3323</v>
+        <v>0.3874</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4951</v>
+        <v>-0.9577</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1628</v>
+        <v>1.3451</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5665</v>
+        <v>-0.27</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0352</v>
+        <v>-0.8283</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5313</v>
+        <v>0.5583</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.3515</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5792</v>
+        <v>0.9654</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4397</v>
+        <v>1.1033</v>
       </c>
       <c r="T18" t="n">
-        <v>1.3511</v>
+        <v>0.4135</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0886</v>
+        <v>0.6898</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2856</v>
+        <v>-1.8415</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2856</v>
+        <v>-1.8415</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1499</v>
+        <v>-2.0175</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.5892</v>
+        <v>-2.3824</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4394</v>
+        <v>0.3649</v>
       </c>
       <c r="G19" t="n">
         <v>-1.1901</v>
@@ -1936,13 +1936,13 @@
         <v>0.1931</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1874</v>
+        <v>-0.0551</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5518</v>
+        <v>-0.345</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3644</v>
+        <v>0.2899</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. BOONYASITH</t>
+          <t>G. MUKENDI KABANGA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7793</v>
+        <v>-2.9637</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6966</v>
+        <v>-1.8428</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0826</v>
+        <v>-1.1209</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9087</v>
+        <v>-1.8988</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6208</v>
+        <v>-1.5303</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7121</v>
+        <v>-0.3685</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1722</v>
+        <v>-0.3323</v>
       </c>
       <c r="K20" t="n">
-        <v>2.5873</v>
+        <v>-0.4951</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.4151</v>
+        <v>0.1628</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2635</v>
+        <v>-1.5665</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9665</v>
+        <v>-1.0352</v>
       </c>
       <c r="O20" t="n">
-        <v>0.703</v>
+        <v>-0.5313</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9654</v>
+        <v>-1.3515</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9654</v>
+        <v>0.5792</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4949</v>
+        <v>0.5723</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9381</v>
+        <v>0.4203</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5568</v>
+        <v>0.152</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2277</v>
+        <v>-0.2856</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2277</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="21">
@@ -2047,22 +2047,22 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>12.3652</v>
+        <v>13.0547</v>
       </c>
       <c r="E21" t="n">
-        <v>9.707599999999998</v>
+        <v>9.707499999999996</v>
       </c>
       <c r="F21" t="n">
-        <v>2.6578</v>
+        <v>3.3472</v>
       </c>
       <c r="G21" t="n">
-        <v>7.4143</v>
+        <v>7.414300000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0006999999999992568</v>
+        <v>-0.0006999999999988127</v>
       </c>
       <c r="I21" t="n">
-        <v>7.415100000000001</v>
+        <v>7.4151</v>
       </c>
       <c r="J21" t="n">
         <v>11.1147</v>
@@ -2071,7 +2071,7 @@
         <v>7.2485</v>
       </c>
       <c r="L21" t="n">
-        <v>3.8662</v>
+        <v>3.866199999999999</v>
       </c>
       <c r="M21" t="n">
         <v>-3.7005</v>
@@ -2089,16 +2089,16 @@
         <v>-10.6194</v>
       </c>
       <c r="R21" t="n">
-        <v>9.6539</v>
+        <v>9.653899999999998</v>
       </c>
       <c r="S21" t="n">
-        <v>4.2753</v>
+        <v>4.9646</v>
       </c>
       <c r="T21" t="n">
-        <v>3.444399999999999</v>
+        <v>3.4444</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8306</v>
+        <v>1.5202</v>
       </c>
       <c r="V21" t="n">
         <v>1.6412</v>
@@ -2107,7 +2107,7 @@
         <v>5.7675</v>
       </c>
       <c r="X21" t="n">
-        <v>-4.126300000000001</v>
+        <v>-4.1263</v>
       </c>
     </row>
   </sheetData>
